--- a/data/trans_camb/P16A08-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P16A08-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 1,9</t>
+          <t>-0,97; 1,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 2,67</t>
+          <t>-0,49; 2,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 3,51</t>
+          <t>-0,3; 3,56</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,55; 4,46</t>
+          <t>0,48; 4,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 3,38</t>
+          <t>-0,43; 3,13</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,1</t>
+          <t>0,24; 4,02</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,69</t>
+          <t>0,16; 2,6</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,14; 2,38</t>
+          <t>0,09; 2,51</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,14</t>
+          <t>0,67; 3,36</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-46,68; 171,29</t>
+          <t>-43,6; 166,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-23,58; 236,91</t>
+          <t>-25,83; 236,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-13,41; 321,91</t>
+          <t>-17,41; 321,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,55; 301,27</t>
+          <t>13,0; 301,4</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-22,21; 216,59</t>
+          <t>-15,66; 221,02</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,46; 300,99</t>
+          <t>3,73; 286,68</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,2; 187,97</t>
+          <t>5,9; 186,49</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,51; 163,35</t>
+          <t>-1,65; 178,12</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>21,42; 215,38</t>
+          <t>22,01; 227,61</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 2,82</t>
+          <t>-0,47; 2,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 1,77</t>
+          <t>-1,18; 1,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 2,21</t>
+          <t>-1,76; 2,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 3,93</t>
+          <t>0,23; 4,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 4,13</t>
+          <t>0,15; 3,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 1,65</t>
+          <t>-1,75; 1,45</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,88</t>
+          <t>0,3; 2,86</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,46</t>
+          <t>0,01; 2,6</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 1,38</t>
+          <t>-1,41; 1,39</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-20,13; 167,28</t>
+          <t>-20,48; 165,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-36,4; 106,21</t>
+          <t>-37,86; 110,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-49,75; 126,01</t>
+          <t>-54,31; 122,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 139,0</t>
+          <t>4,55; 135,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,22; 140,9</t>
+          <t>1,03; 133,98</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-36,04; 60,13</t>
+          <t>-38,05; 51,48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,95; 114,92</t>
+          <t>8,76; 116,98</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 97,58</t>
+          <t>-0,17; 103,03</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-34,53; 54,45</t>
+          <t>-36,83; 56,5</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,11; 4,33</t>
+          <t>-0,06; 3,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 2,56</t>
+          <t>-0,93; 2,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,43; 4,69</t>
+          <t>0,37; 4,8</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 3,73</t>
+          <t>-1,08; 3,63</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,14; 5,05</t>
+          <t>0,3; 4,97</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 1,94</t>
+          <t>-2,97; 1,92</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,14; 3,22</t>
+          <t>0,22; 3,16</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 3,15</t>
+          <t>0,18; 3,06</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 2,54</t>
+          <t>-0,95; 2,5</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 320,56</t>
+          <t>-11,13; 248,17</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-34,29; 176,84</t>
+          <t>-30,44; 184,88</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,32; 343,09</t>
+          <t>2,58; 328,3</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-21,57; 109,27</t>
+          <t>-20,38; 107,77</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 156,47</t>
+          <t>3,4; 146,7</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-59,14; 53,42</t>
+          <t>-56,35; 53,35</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,98; 125,48</t>
+          <t>2,97; 123,59</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4,59; 119,6</t>
+          <t>3,26; 115,28</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-20,93; 95,86</t>
+          <t>-23,08; 89,43</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 2,31</t>
+          <t>-1,0; 2,42</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 2,32</t>
+          <t>-1,07; 2,32</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 1,75</t>
+          <t>-1,65; 1,82</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 2,73</t>
+          <t>-1,34; 2,79</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 1,78</t>
+          <t>-1,99; 1,87</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 23,16</t>
+          <t>0,02; 24,37</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 2,11</t>
+          <t>-0,64; 2,04</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 1,49</t>
+          <t>-1,11; 1,61</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 16,38</t>
+          <t>-0,08; 15,65</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-27,09; 108,35</t>
+          <t>-26,05; 107,52</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-27,95; 100,92</t>
+          <t>-28,29; 98,4</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-46,39; 81,14</t>
+          <t>-44,27; 83,23</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-23,71; 65,38</t>
+          <t>-22,3; 72,4</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-35,44; 43,17</t>
+          <t>-33,41; 52,15</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 539,64</t>
+          <t>0,38; 546,89</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-12,9; 60,91</t>
+          <t>-12,86; 59,77</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-21,82; 45,82</t>
+          <t>-24,01; 47,16</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 475,31</t>
+          <t>-2,63; 438,33</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,88</t>
+          <t>0,18; 1,85</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 1,4</t>
+          <t>-0,06; 1,57</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 1,86</t>
+          <t>-0,12; 1,88</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,62; 2,67</t>
+          <t>0,65; 2,6</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,56</t>
+          <t>0,4; 2,44</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,25; 8,91</t>
+          <t>0,23; 9,71</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,65; 1,98</t>
+          <t>0,63; 2,02</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,42; 1,74</t>
+          <t>0,46; 1,82</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,43; 5,37</t>
+          <t>0,47; 4,89</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>7,65; 96,05</t>
+          <t>5,3; 91,58</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-10,18; 68,55</t>
+          <t>-2,85; 80,58</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-6,43; 91,51</t>
+          <t>-4,78; 91,82</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>14,64; 80,68</t>
+          <t>14,54; 73,49</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>11,81; 75,47</t>
+          <t>9,13; 71,14</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5,96; 253,6</t>
+          <t>4,68; 235,28</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>19,21; 69,95</t>
+          <t>18,32; 72,09</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>11,56; 59,29</t>
+          <t>12,58; 62,45</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>12,63; 164,9</t>
+          <t>14,3; 158,08</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A08-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P16A08-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,58</t>
+          <t>1,48</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,16</t>
+          <t>2,11</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1,89</t>
+          <t>1,81</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 1,95</t>
+          <t>-1,03; 1,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 2,79</t>
+          <t>-0,59; 2,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 3,56</t>
+          <t>-0,16; 3,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,18</t>
+          <t>0,57; 4,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 3,13</t>
+          <t>-0,28; 3,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,24; 4,02</t>
+          <t>0,42; 4,03</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,16; 2,6</t>
+          <t>0,25; 2,57</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,09; 2,51</t>
+          <t>-0,01; 2,36</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,67; 3,36</t>
+          <t>0,49; 3,16</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>99,95%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>93,18%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-43,6; 166,79</t>
+          <t>-46,85; 169,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-25,83; 236,63</t>
+          <t>-28,42; 252,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-17,41; 321,05</t>
+          <t>-12,78; 307,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,0; 301,4</t>
+          <t>16,77; 293,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-15,66; 221,02</t>
+          <t>-13,51; 233,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,73; 286,68</t>
+          <t>10,13; 275,76</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,9; 186,49</t>
+          <t>7,46; 175,6</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 178,12</t>
+          <t>-2,43; 162,38</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>22,01; 227,61</t>
+          <t>18,04; 213,43</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,28</t>
+          <t>0,71</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,07</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>0,39</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 2,73</t>
+          <t>-0,45; 2,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 1,99</t>
+          <t>-1,12; 2,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 2,19</t>
+          <t>-0,76; 2,63</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,23; 4,04</t>
+          <t>0,19; 4,12</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,15; 3,94</t>
+          <t>0,29; 4,21</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 1,45</t>
+          <t>-1,62; 1,6</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,86</t>
+          <t>0,34; 2,92</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,01; 2,6</t>
+          <t>0,01; 2,51</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 1,39</t>
+          <t>-0,67; 1,72</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-1,8%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>12,58%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-20,48; 165,9</t>
+          <t>-14,66; 167,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-37,86; 110,15</t>
+          <t>-37,49; 124,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-54,31; 122,18</t>
+          <t>-28,32; 148,97</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,55; 135,12</t>
+          <t>4,05; 138,95</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,03; 133,98</t>
+          <t>4,44; 147,79</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-38,05; 51,48</t>
+          <t>-34,71; 60,25</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,76; 116,98</t>
+          <t>8,7; 119,85</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 103,03</t>
+          <t>-0,99; 103,92</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-36,83; 56,5</t>
+          <t>-18,61; 74,14</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,35</t>
+          <t>2,09</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-0,24</t>
+          <t>1,71</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1,02</t>
+          <t>1,9</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 3,87</t>
+          <t>0,04; 4,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 2,61</t>
+          <t>-0,82; 2,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,37; 4,8</t>
+          <t>0,31; 4,56</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 3,63</t>
+          <t>-0,94; 3,75</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,3; 4,97</t>
+          <t>0,13; 4,76</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 1,92</t>
+          <t>-0,56; 3,99</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,22; 3,16</t>
+          <t>0,23; 3,3</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,18; 3,06</t>
+          <t>0,25; 3,21</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 2,5</t>
+          <t>0,54; 3,44</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>108,0%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-5,48%</t>
+          <t>39,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>58,39%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-11,13; 248,17</t>
+          <t>-4,6; 272,36</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-30,44; 184,88</t>
+          <t>-28,86; 195,68</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,58; 328,3</t>
+          <t>3,67; 313,95</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-20,38; 107,77</t>
+          <t>-19,11; 118,79</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,4; 146,7</t>
+          <t>0,53; 143,66</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-56,35; 53,35</t>
+          <t>-11,12; 122,69</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,97; 123,59</t>
+          <t>3,94; 126,58</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,26; 115,28</t>
+          <t>5,99; 125,49</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-23,08; 89,43</t>
+          <t>12,41; 140,75</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-0,01</t>
+          <t>0,08</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,68</t>
+          <t>0,76</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3,64</t>
+          <t>0,45</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 2,42</t>
+          <t>-1,08; 2,45</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 2,32</t>
+          <t>-1,04; 2,31</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 1,82</t>
+          <t>-1,55; 1,68</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 2,79</t>
+          <t>-1,2; 2,84</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 1,87</t>
+          <t>-2,0; 2,01</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,02; 24,37</t>
+          <t>-1,11; 2,62</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 2,04</t>
+          <t>-0,65; 2,08</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 1,61</t>
+          <t>-1,02; 1,74</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 15,65</t>
+          <t>-0,82; 1,67</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-0,34%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>133,76%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>11,1%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-26,05; 107,52</t>
+          <t>-29,7; 115,14</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-28,29; 98,4</t>
+          <t>-28,63; 102,16</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-44,27; 83,23</t>
+          <t>-41,97; 70,54</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-22,3; 72,4</t>
+          <t>-21,03; 73,84</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-33,41; 52,15</t>
+          <t>-33,05; 49,89</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,38; 546,89</t>
+          <t>-18,37; 67,89</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-12,86; 59,77</t>
+          <t>-14,53; 60,58</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-24,01; 47,16</t>
+          <t>-22,06; 49,97</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 438,33</t>
+          <t>-17,03; 49,49</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0,87</t>
+          <t>1,0</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,36</t>
+          <t>1,04</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1,65</t>
+          <t>1,03</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,85</t>
+          <t>0,18; 1,87</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 1,57</t>
+          <t>-0,06; 1,49</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 1,88</t>
+          <t>0,21; 1,9</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,6</t>
+          <t>0,59; 2,64</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,4; 2,44</t>
+          <t>0,42; 2,45</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,23; 9,71</t>
+          <t>0,2; 1,99</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,02</t>
+          <t>0,63; 1,99</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,46; 1,82</t>
+          <t>0,47; 1,74</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,89</t>
+          <t>0,44; 1,67</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>41,78%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>60,42%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>52,11%</t>
+          <t>32,52%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>5,3; 91,58</t>
+          <t>6,84; 94,11</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 80,58</t>
+          <t>-3,24; 73,57</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 91,82</t>
+          <t>6,55; 97,89</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>14,54; 73,49</t>
+          <t>12,61; 75,44</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>9,13; 71,14</t>
+          <t>9,21; 70,27</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,68; 235,28</t>
+          <t>4,44; 60,77</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>18,32; 72,09</t>
+          <t>18,32; 69,79</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>12,58; 62,45</t>
+          <t>13,65; 61,64</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>14,3; 158,08</t>
+          <t>12,79; 58,1</t>
         </is>
       </c>
     </row>
